--- a/data/trans_orig/P24E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P24E-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2007</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2007 (tasa de respuesta: 98,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29808</t>
+          <t>29383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22237</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40054</t>
+          <t>40857</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33136</t>
+          <t>33433</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51321</t>
+          <t>50390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>18768</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46026</t>
+          <t>46181</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65803</t>
+          <t>66058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,02%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21386</t>
+          <t>22264</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>27404</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28495</t>
+          <t>27172</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50333</t>
+          <t>50590</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21549</t>
+          <t>20259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40083</t>
+          <t>39843</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53050</t>
+          <t>55004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>83533</t>
+          <t>83735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53298</t>
+          <t>53982</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77284</t>
+          <t>77472</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42155</t>
+          <t>43007</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62312</t>
+          <t>63231</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101872</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>133389</t>
+          <t>133420</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30006</t>
+          <t>30023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23371</t>
+          <t>23300</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44281</t>
+          <t>44392</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22273</t>
+          <t>22400</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42203</t>
+          <t>42815</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33973</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>45730</t>
+          <t>45555</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71190</t>
+          <t>71203</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,59%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40174</t>
+          <t>39335</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59784</t>
+          <t>60142</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>21012</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37882</t>
+          <t>37544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67552</t>
+          <t>67071</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93114</t>
+          <t>93194</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15935</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16952</t>
+          <t>16735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28611</t>
+          <t>27231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33683</t>
+          <t>33670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53673</t>
+          <t>54269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33533</t>
+          <t>33204</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54088</t>
+          <t>54197</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72878</t>
+          <t>69265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101765</t>
+          <t>100517</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,04%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49004</t>
+          <t>49828</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69618</t>
+          <t>69436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>36753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56266</t>
+          <t>56596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>91751</t>
+          <t>92097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121739</t>
+          <t>122581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25378</t>
+          <t>25553</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20580</t>
+          <t>21127</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43027</t>
+          <t>42433</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115310</t>
+          <t>115202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155553</t>
+          <t>154693</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94344</t>
+          <t>91047</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128178</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219819</t>
+          <t>220511</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>271533</t>
+          <t>268912</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>197991</t>
+          <t>196442</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>238429</t>
+          <t>237532</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>124717</t>
+          <t>126402</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>159573</t>
+          <t>160390</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>332451</t>
+          <t>334467</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>388284</t>
+          <t>386100</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43792</t>
+          <t>44367</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72190</t>
+          <t>70966</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57785</t>
+          <t>57336</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82775</t>
+          <t>85426</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122082</t>
+          <t>122191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2012</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2012 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42458</t>
+          <t>43828</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65174</t>
+          <t>65356</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32529</t>
+          <t>32444</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54025</t>
+          <t>51827</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79856</t>
+          <t>83211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110832</t>
+          <t>112241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48315</t>
+          <t>48788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71831</t>
+          <t>71694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32187</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53728</t>
+          <t>53616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88096</t>
+          <t>87541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119250</t>
+          <t>118445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24419</t>
+          <t>24168</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17324</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35513</t>
+          <t>35841</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62490</t>
+          <t>61326</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91730</t>
+          <t>90744</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61705</t>
+          <t>61054</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85979</t>
+          <t>85776</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130277</t>
+          <t>130021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169175</t>
+          <t>170696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>82297</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>112691</t>
+          <t>112504</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51865</t>
+          <t>51951</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76715</t>
+          <t>75530</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>140997</t>
+          <t>139618</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>179852</t>
+          <t>179961</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>15222</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35094</t>
+          <t>36380</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>19848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24983</t>
+          <t>25390</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49741</t>
+          <t>50567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40146</t>
+          <t>39762</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63637</t>
+          <t>64208</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32602</t>
+          <t>33048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54881</t>
+          <t>54753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78589</t>
+          <t>80278</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>111397</t>
+          <t>111694</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60494</t>
+          <t>60453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86519</t>
+          <t>86026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39500</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61612</t>
+          <t>61106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106651</t>
+          <t>104940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140596</t>
+          <t>139991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31518</t>
+          <t>31611</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30258</t>
+          <t>30477</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30617</t>
+          <t>30183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>55614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47262</t>
+          <t>46469</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71884</t>
+          <t>69881</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52484</t>
+          <t>53021</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76111</t>
+          <t>75789</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105081</t>
+          <t>105261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138784</t>
+          <t>139906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55087</t>
+          <t>57524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80550</t>
+          <t>81228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34522</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56437</t>
+          <t>56835</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97541</t>
+          <t>96875</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131570</t>
+          <t>130251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31607</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>33179</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>31966</t>
+          <t>31614</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56140</t>
+          <t>57547</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213993</t>
+          <t>215990</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266205</t>
+          <t>265488</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201680</t>
+          <t>200851</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246549</t>
+          <t>246045</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>429150</t>
+          <t>428935</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>497431</t>
+          <t>497483</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>271644</t>
+          <t>272930</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>325231</t>
+          <t>325611</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>180332</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>224289</t>
+          <t>226940</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>466350</t>
+          <t>463343</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>534788</t>
+          <t>534896</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65214</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103380</t>
+          <t>102087</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49757</t>
+          <t>49942</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81177</t>
+          <t>81211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121106</t>
+          <t>124035</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171414</t>
+          <t>173376</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2016</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2016 (tasa de respuesta: 98,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15486</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33007</t>
+          <t>32458</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>28199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33425</t>
+          <t>34002</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55421</t>
+          <t>55752</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52451</t>
+          <t>52446</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73248</t>
+          <t>72853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26182</t>
+          <t>27107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42140</t>
+          <t>42352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85020</t>
+          <t>85008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110566</t>
+          <t>110061</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,01%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32807</t>
+          <t>32079</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>16515</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>23432</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45527</t>
+          <t>43465</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26373</t>
+          <t>26139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49449</t>
+          <t>48890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27065</t>
+          <t>26825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47563</t>
+          <t>48675</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>59733</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>89731</t>
+          <t>91679</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71155</t>
+          <t>71528</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96562</t>
+          <t>97505</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68575</t>
+          <t>69219</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93102</t>
+          <t>91520</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>147791</t>
+          <t>146836</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>181756</t>
+          <t>182425</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,99%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>24759</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46544</t>
+          <t>45690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31303</t>
+          <t>30792</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42840</t>
+          <t>42631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70536</t>
+          <t>71505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24239</t>
+          <t>24015</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45696</t>
+          <t>44513</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>16748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33727</t>
+          <t>31837</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46201</t>
+          <t>45113</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71481</t>
+          <t>71524</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51866</t>
+          <t>51998</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74732</t>
+          <t>73688</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26036</t>
+          <t>27546</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44427</t>
+          <t>43502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85982</t>
+          <t>84997</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112553</t>
+          <t>112245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,37%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25476</t>
+          <t>23545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38002</t>
+          <t>37615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28932</t>
+          <t>28779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49387</t>
+          <t>49162</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30020</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64687</t>
+          <t>64569</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94319</t>
+          <t>93574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,29%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50826</t>
+          <t>51982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72482</t>
+          <t>73145</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46221</t>
+          <t>45664</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68295</t>
+          <t>67868</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>103929</t>
+          <t>104346</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134049</t>
+          <t>134726</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32734</t>
+          <t>31608</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16842</t>
+          <t>17179</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34256</t>
+          <t>34627</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35484</t>
+          <t>35247</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60165</t>
+          <t>59258</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111933</t>
+          <t>111111</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151632</t>
+          <t>151715</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105213</t>
+          <t>106998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142770</t>
+          <t>144340</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>228457</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>282473</t>
+          <t>285309</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>248920</t>
+          <t>250610</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>295590</t>
+          <t>296246</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>188023</t>
+          <t>188183</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>229106</t>
+          <t>228262</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>450321</t>
+          <t>446226</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>511905</t>
+          <t>508088</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76988</t>
+          <t>78666</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113660</t>
+          <t>114770</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51522</t>
+          <t>53106</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82170</t>
+          <t>82676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>138850</t>
+          <t>139632</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>185624</t>
+          <t>186144</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P24E-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>14580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29383</t>
+          <t>30364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14798</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22616</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40857</t>
+          <t>40076</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33433</t>
+          <t>33984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50390</t>
+          <t>50317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18768</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46181</t>
+          <t>45411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66058</t>
+          <t>66319</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,26%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8246</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22264</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>27998</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>26639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50590</t>
+          <t>48467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20259</t>
+          <t>21230</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39843</t>
+          <t>39556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55004</t>
+          <t>55241</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>83735</t>
+          <t>83140</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53982</t>
+          <t>54118</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77472</t>
+          <t>77703</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43007</t>
+          <t>42861</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63231</t>
+          <t>62467</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>103103</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>133420</t>
+          <t>132428</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,35%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30023</t>
+          <t>29960</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>23103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44392</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>22619</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42815</t>
+          <t>43299</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>18313</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34239</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>45308</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71203</t>
+          <t>71339</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39335</t>
+          <t>38752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60142</t>
+          <t>59790</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21012</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37544</t>
+          <t>37859</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>66921</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93194</t>
+          <t>92443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,19%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>17399</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16735</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>11456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27231</t>
+          <t>28027</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33670</t>
+          <t>33305</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54269</t>
+          <t>53100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33204</t>
+          <t>32751</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54197</t>
+          <t>54706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69265</t>
+          <t>71725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100517</t>
+          <t>100776</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49828</t>
+          <t>50046</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69436</t>
+          <t>70861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36753</t>
+          <t>36490</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56596</t>
+          <t>57739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92097</t>
+          <t>92441</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122581</t>
+          <t>121079</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21410</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>25784</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>21114</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42433</t>
+          <t>41833</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115202</t>
+          <t>115170</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>154693</t>
+          <t>152688</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>91047</t>
+          <t>93203</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>125986</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>220511</t>
+          <t>217737</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>268912</t>
+          <t>269655</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>196442</t>
+          <t>196836</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>237532</t>
+          <t>238911</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>126402</t>
+          <t>126131</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>160390</t>
+          <t>160085</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>334467</t>
+          <t>333651</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>386100</t>
+          <t>385319</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44367</t>
+          <t>43852</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70966</t>
+          <t>70992</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>32582</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>56523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85426</t>
+          <t>83295</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122191</t>
+          <t>119417</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43828</t>
+          <t>43512</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65356</t>
+          <t>66494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32444</t>
+          <t>32041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51827</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83211</t>
+          <t>79032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112241</t>
+          <t>111375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48788</t>
+          <t>47747</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71694</t>
+          <t>71885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53616</t>
+          <t>52977</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87541</t>
+          <t>88742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118445</t>
+          <t>119496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24168</t>
+          <t>24505</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18232</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15604</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35841</t>
+          <t>37469</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61326</t>
+          <t>61157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90744</t>
+          <t>91213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61054</t>
+          <t>61150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85776</t>
+          <t>86018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130021</t>
+          <t>131319</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>170696</t>
+          <t>168811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82297</t>
+          <t>82651</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>112504</t>
+          <t>112662</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51951</t>
+          <t>51496</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75530</t>
+          <t>75633</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>139618</t>
+          <t>141826</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>179961</t>
+          <t>180098</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36380</t>
+          <t>35798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50567</t>
+          <t>49164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39762</t>
+          <t>39897</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64208</t>
+          <t>65476</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33048</t>
+          <t>33571</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54753</t>
+          <t>56014</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>80278</t>
+          <t>79073</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>111694</t>
+          <t>111750</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60453</t>
+          <t>60910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86026</t>
+          <t>86849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38605</t>
+          <t>39050</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61106</t>
+          <t>61455</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104940</t>
+          <t>105387</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139991</t>
+          <t>140987</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31611</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30477</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>28995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55614</t>
+          <t>55559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46469</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69881</t>
+          <t>70769</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53021</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75789</t>
+          <t>76757</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105261</t>
+          <t>105588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139906</t>
+          <t>137573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57524</t>
+          <t>55746</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81228</t>
+          <t>80498</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34965</t>
+          <t>34128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56835</t>
+          <t>56620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>96875</t>
+          <t>98432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130251</t>
+          <t>130679</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,7%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31496</t>
+          <t>31458</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33179</t>
+          <t>32793</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>31614</t>
+          <t>31120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57547</t>
+          <t>57850</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215990</t>
+          <t>213582</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265488</t>
+          <t>264725</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>200851</t>
+          <t>200931</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246045</t>
+          <t>247267</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>428935</t>
+          <t>430851</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>497483</t>
+          <t>495545</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>272930</t>
+          <t>273722</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>325611</t>
+          <t>326506</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>180426</t>
+          <t>178526</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>226940</t>
+          <t>225084</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>463343</t>
+          <t>464306</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>534896</t>
+          <t>534862</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>63989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>102087</t>
+          <t>101872</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49942</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81211</t>
+          <t>81714</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124035</t>
+          <t>124755</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>173376</t>
+          <t>171650</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15767</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32458</t>
+          <t>33407</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28199</t>
+          <t>28289</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34002</t>
+          <t>34014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55752</t>
+          <t>57805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52446</t>
+          <t>52504</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72853</t>
+          <t>75174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27107</t>
+          <t>27180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42352</t>
+          <t>43323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85008</t>
+          <t>82174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110061</t>
+          <t>110273</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>15295</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32079</t>
+          <t>32612</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23432</t>
+          <t>23859</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43465</t>
+          <t>44142</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26139</t>
+          <t>26048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48890</t>
+          <t>49156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>27359</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48675</t>
+          <t>47911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59733</t>
+          <t>59560</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91679</t>
+          <t>90177</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71528</t>
+          <t>71512</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97505</t>
+          <t>97552</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69219</t>
+          <t>68216</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91520</t>
+          <t>92019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>146836</t>
+          <t>144847</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>182425</t>
+          <t>180864</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,46%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24759</t>
+          <t>24641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45690</t>
+          <t>46280</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30792</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42631</t>
+          <t>42036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71505</t>
+          <t>71156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24015</t>
+          <t>23747</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44513</t>
+          <t>44640</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16748</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31837</t>
+          <t>33264</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>45113</t>
+          <t>45131</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71524</t>
+          <t>71313</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51998</t>
+          <t>52655</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73688</t>
+          <t>74007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27546</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43502</t>
+          <t>43883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84997</t>
+          <t>84418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112245</t>
+          <t>113354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,98%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>24216</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>18005</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37615</t>
+          <t>36745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28779</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49162</t>
+          <t>49883</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30070</t>
+          <t>29893</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51731</t>
+          <t>53318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64569</t>
+          <t>65999</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93574</t>
+          <t>96147</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51982</t>
+          <t>50988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73145</t>
+          <t>72613</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45664</t>
+          <t>44705</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67868</t>
+          <t>67978</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104346</t>
+          <t>103517</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134726</t>
+          <t>134662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14313</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31608</t>
+          <t>32637</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17179</t>
+          <t>16633</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34627</t>
+          <t>34304</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35247</t>
+          <t>35747</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59258</t>
+          <t>59735</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111111</t>
+          <t>112301</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151715</t>
+          <t>153223</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>106998</t>
+          <t>105375</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>144340</t>
+          <t>143671</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>228457</t>
+          <t>227844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>285309</t>
+          <t>282334</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>250610</t>
+          <t>249457</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>296246</t>
+          <t>296038</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>188183</t>
+          <t>185637</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>228262</t>
+          <t>226477</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>446226</t>
+          <t>449474</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>508088</t>
+          <t>507467</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78666</t>
+          <t>77332</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>114770</t>
+          <t>114282</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53106</t>
+          <t>52787</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82676</t>
+          <t>82557</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139632</t>
+          <t>139417</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>186144</t>
+          <t>186232</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
